--- a/static/standards-correlations/Idaho_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Idaho_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$55</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Idaho 9-12 CS Standards, Draft 2 dated 03/28/2024</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Idaho 9-12 CS Standards, Draft 2 dated 03/28/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -753,7 +754,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>The Wombat is an embedded controller and Ext 3.1E (Computer vs. Peripheral) makes that explicit. Discovery Systems 2 extends to embedded computing in everyday objects.</t>
+          <t>The Wombat is an embedded controller and Ext 3.1E (Computer vs. Peripheral) makes that explicit. Introductory Systems 2 extends to embedded computing in everyday objects.</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1255,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Ext 5.3E (Ethical Use and the Rules) puts students against the school Acceptable Use Policy and the ethics of copying unlicensed work, alongside the Discovery digital-citizenship projects.</t>
+          <t>Ext 5.3E (Ethical Use and the Rules) puts students against the school Acceptable Use Policy and the ethics of copying unlicensed work, alongside the Introductory digital-citizenship projects.</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1850,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Discovery Systems 9 covers protocols. Routers, switches, and topology are absent.</t>
+          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Introductory Systems 9 covers protocols. Routers, switches, and topology are absent.</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2504,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Botball Explorer is team-based by design, and Discovery Systems 13 rotates students through defined roles including lead.</t>
+          <t>Botball Explorer is team-based by design, and Introductory Systems 13 rotates students through defined roles including lead.</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2641,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Role rotation surfaces different strengths and Discovery Systems 13 asks what a team loses when one person always drives. Diversity in the broader sense is not addressed.</t>
+          <t>Role rotation surfaces different strengths and Introductory Systems 13 asks what a team loses when one person always drives. Diversity in the broader sense is not addressed.</t>
         </is>
       </c>
     </row>
@@ -2975,6 +2976,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -3019,7 +3021,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3033,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -3131,6 +3133,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -3148,7 +3152,7 @@
 ENTRY-LEVEL COURSE: House Bill 648 (2018) requires Idaho districts to make one or more computer science courses available to all high school students. Idaho does not name a single entry-level course, so the 9-12 band is the target.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met. Cells citing 'Ext N.NL' identify the specific extension so a reviewer can verify placement.</t>
         </is>
       </c>
